--- a/public/plantilla-registro-fotografico.xlsx
+++ b/public/plantilla-registro-fotografico.xlsx
@@ -526,7 +526,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -754,6 +754,24 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1211,7 +1229,7 @@
     <tabColor theme="4" tint="0.3999755851924192"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.77734375" customWidth="1" style="27" min="1" max="2"/>
@@ -1705,174 +1723,307 @@
       <c r="K26" s="25" t="n"/>
       <c r="L26" s="22" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="27">
-      <c r="A27" s="94" t="inlineStr">
+    <row r="27" ht="16.95" customHeight="1" s="27">
+      <c r="A27" s="80" t="inlineStr">
+        <is>
+          <t>FOTO 5</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="80" t="inlineStr">
+        <is>
+          <t>FOTO 6</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+      <c r="L27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="199.95" customHeight="1" s="27">
+      <c r="A28" s="89" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="89" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="19.95" customHeight="1" s="27">
+      <c r="A29" s="88" t="inlineStr">
+        <is>
+          <t>Aspecto</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="88" t="inlineStr">
+        <is>
+          <t>Aspecto</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="32" t="n"/>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="28.05" customHeight="1" s="27">
+      <c r="A30" s="88" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="88" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="19.95" customHeight="1" s="27">
+      <c r="A31" s="88" t="inlineStr">
+        <is>
+          <t>Coordenadas</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="88" t="inlineStr">
+        <is>
+          <t>Coordenadas</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="32" t="n"/>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="25" t="n"/>
+      <c r="L31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="19.95" customHeight="1" s="27">
+      <c r="A32" s="88" t="inlineStr">
+        <is>
+          <t>Fecha y hora</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="88" t="inlineStr">
+        <is>
+          <t>Fecha y hora</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="32" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="27">
+      <c r="A33" s="94" t="inlineStr">
         <is>
           <t>Las coordenadas (latitud, longitud) las toma el celular al hacer la foto. Una foto por recuadro, sin recortar ni editar.</t>
         </is>
       </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="25" t="n"/>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="25" t="n"/>
-      <c r="L27" s="22" t="n"/>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" s="27">
-      <c r="A28" s="77" t="inlineStr">
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="25" t="n"/>
+      <c r="D33" s="25" t="n"/>
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="25" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="25" t="n"/>
+      <c r="L33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="27">
+      <c r="A34" s="77" t="inlineStr">
         <is>
           <t>3. FIRMAS</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="17" t="n"/>
-      <c r="L28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" s="27">
-      <c r="A29" s="81" t="inlineStr">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="18" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="27">
+      <c r="A35" s="81" t="inlineStr">
         <is>
           <t>REGISTRÓ — RESPONSABLE AMBIENTAL</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="21" t="n"/>
-      <c r="G29" s="81" t="inlineStr">
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="81" t="inlineStr">
         <is>
           <t>REVISÓ — RESIDENTE DE OBRA</t>
         </is>
       </c>
-      <c r="H29" s="20" t="n"/>
-      <c r="I29" s="20" t="n"/>
-      <c r="J29" s="20" t="n"/>
-      <c r="K29" s="20" t="n"/>
-      <c r="L29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="42" customHeight="1" s="27">
-      <c r="A30" s="82" t="inlineStr">
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="20" t="n"/>
+      <c r="K35" s="20" t="n"/>
+      <c r="L35" s="21" t="n"/>
+    </row>
+    <row r="36" ht="42" customHeight="1" s="27">
+      <c r="A36" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="18" t="n"/>
-      <c r="G30" s="82" t="inlineStr">
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="H30" s="18" t="n"/>
-      <c r="I30" s="19" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="17" t="n"/>
-      <c r="L30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="21" customHeight="1" s="27">
-      <c r="A31" s="82" t="inlineStr">
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="19" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="17" t="n"/>
+      <c r="L36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="21" customHeight="1" s="27">
+      <c r="A37" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="82" t="inlineStr">
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="17" t="n"/>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="18" t="n"/>
-    </row>
-    <row r="32" ht="21" customHeight="1" s="27">
-      <c r="A32" s="82" t="inlineStr">
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="19" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="18" t="n"/>
+    </row>
+    <row r="38" ht="21" customHeight="1" s="27">
+      <c r="A38" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="82" t="inlineStr">
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="19" t="n"/>
-      <c r="J32" s="17" t="n"/>
-      <c r="K32" s="17" t="n"/>
-      <c r="L32" s="18" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="19" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="17" t="n"/>
+      <c r="L38" s="18" t="n"/>
+    </row>
+    <row r="39" s="27">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>REV. 08/10/2026</t>
         </is>
       </c>
-      <c r="G33" s="37">
+      <c r="G39" s="37">
         <f>K5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="101">
     <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="I38:L38"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
     <mergeCell ref="D1:L2"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="G18:H18"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="I25:L25"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A34:L34"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="I18:L18"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="K13:L13"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I29:L29"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G38:H38"/>
     <mergeCell ref="I31:L31"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G22:L22"/>
     <mergeCell ref="I32:L32"/>
@@ -1882,42 +2033,53 @@
     <mergeCell ref="I24:L24"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="I17:L17"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="I19:L19"/>
-    <mergeCell ref="G33:L33"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="K11:L11"/>
+    <mergeCell ref="G37:H37"/>
     <mergeCell ref="I30:L30"/>
+    <mergeCell ref="D3:L3"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="G35:L35"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="I37:L37"/>
     <mergeCell ref="K7:L7"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G39:L39"/>
     <mergeCell ref="C11:I11"/>
     <mergeCell ref="I23:L23"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G36:H36"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G15:L15"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A33:L33"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="I36:L36"/>
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="G16:L16"/>
     <mergeCell ref="G30:H30"/>
-    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A9:L9"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="I12:L12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="G31:H31"/>
@@ -1925,7 +2087,7 @@
     <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Página &amp;P de &amp;N</oddFooter>

--- a/public/plantilla-registro-fotografico.xlsx
+++ b/public/plantilla-registro-fotografico.xlsx
@@ -15,6 +15,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="165" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>

--- a/public/plantilla-registro-fotografico.xlsx
+++ b/public/plantilla-registro-fotografico.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="9" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Fotográfico" sheetId="1" state="visible" r:id="rId1"/>
@@ -1239,10 +1239,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.77734375" customWidth="1" style="27" min="1" max="2"/>
-    <col width="9.44140625" customWidth="1" style="27" min="3" max="9"/>
-    <col width="15" customWidth="1" style="27" min="10" max="10"/>
-    <col width="9.44140625" customWidth="1" style="27" min="11" max="12"/>
-    <col width="8.88671875" customWidth="1" style="27" min="13" max="16384"/>
+    <col width="9.78" customWidth="1" style="27" min="3" max="6"/>
+    <col width="10.78" customWidth="1" style="27" min="7" max="9"/>
+    <col width="18.78" customWidth="1" style="27" min="10" max="10"/>
+    <col width="9.78" customWidth="1" style="27" min="11" max="12"/>
+    <col width="8.88671875" customWidth="1" style="27" min="13" max="30"/>
+    <col width="8.88671875" customWidth="1" style="27" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="27">

--- a/public/plantilla-registro-fotografico.xlsx
+++ b/public/plantilla-registro-fotografico.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Fotográfico" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,12 +16,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -166,6 +166,15 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -532,7 +541,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -560,19 +569,19 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -621,7 +630,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -639,7 +648,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -674,7 +683,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -777,6 +786,41 @@
     </xf>
     <xf numFmtId="4" fontId="13" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1239,10 +1283,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.77734375" customWidth="1" style="27" min="1" max="2"/>
-    <col width="9.78" customWidth="1" style="27" min="3" max="6"/>
+    <col width="13" customWidth="1" style="27" min="2" max="2"/>
+    <col width="9.779999999999999" customWidth="1" style="27" min="3" max="6"/>
+    <col width="13" customWidth="1" style="27" min="4" max="4"/>
+    <col width="13" customWidth="1" style="27" min="5" max="5"/>
+    <col width="13" customWidth="1" style="27" min="6" max="6"/>
     <col width="10.78" customWidth="1" style="27" min="7" max="9"/>
+    <col width="13" customWidth="1" style="27" min="8" max="8"/>
+    <col width="13" customWidth="1" style="27" min="9" max="9"/>
     <col width="18.78" customWidth="1" style="27" min="10" max="10"/>
-    <col width="9.78" customWidth="1" style="27" min="11" max="12"/>
+    <col width="9.779999999999999" customWidth="1" style="27" min="11" max="12"/>
+    <col width="13" customWidth="1" style="27" min="12" max="12"/>
     <col width="8.88671875" customWidth="1" style="27" min="13" max="30"/>
     <col width="8.88671875" customWidth="1" style="27" min="31" max="16384"/>
   </cols>
@@ -1402,20 +1453,20 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="22" t="n"/>
+      <c r="C11" s="103" t="n"/>
+      <c r="D11" s="104" t="n"/>
+      <c r="E11" s="104" t="n"/>
+      <c r="F11" s="104" t="n"/>
+      <c r="G11" s="104" t="n"/>
+      <c r="H11" s="104" t="n"/>
+      <c r="I11" s="105" t="n"/>
       <c r="J11" s="88" t="inlineStr">
         <is>
           <t>Hoja N°</t>
         </is>
       </c>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="K11" s="106" t="n"/>
+      <c r="L11" s="105" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="27">
       <c r="A12" s="88" t="inlineStr">
@@ -1424,20 +1475,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="22" t="n"/>
+      <c r="C12" s="103" t="n"/>
+      <c r="D12" s="104" t="n"/>
+      <c r="E12" s="104" t="n"/>
+      <c r="F12" s="105" t="n"/>
       <c r="G12" s="88" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="H12" s="22" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="I12" s="103" t="n"/>
+      <c r="J12" s="104" t="n"/>
+      <c r="K12" s="104" t="n"/>
+      <c r="L12" s="105" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="27">
       <c r="A13" s="88" t="inlineStr">
@@ -1446,24 +1497,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="107" t="n"/>
+      <c r="D13" s="105" t="n"/>
       <c r="E13" s="88" t="inlineStr">
         <is>
           <t>Tipo de registro</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="32" t="n"/>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="22" t="n"/>
+      <c r="G13" s="106" t="n"/>
+      <c r="H13" s="104" t="n"/>
+      <c r="I13" s="105" t="n"/>
       <c r="J13" s="88" t="inlineStr">
         <is>
           <t>Registró</t>
         </is>
       </c>
-      <c r="K13" s="24" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="103" t="n"/>
+      <c r="L13" s="105" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="27">
       <c r="A14" s="77" t="inlineStr">
@@ -1506,18 +1557,18 @@
       <c r="L15" s="21" t="n"/>
     </row>
     <row r="16" ht="199.95" customHeight="1" s="27">
-      <c r="A16" s="89" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="89" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="22" t="n"/>
+      <c r="A16" s="108" t="n"/>
+      <c r="B16" s="104" t="n"/>
+      <c r="C16" s="104" t="n"/>
+      <c r="D16" s="104" t="n"/>
+      <c r="E16" s="104" t="n"/>
+      <c r="F16" s="105" t="n"/>
+      <c r="G16" s="108" t="n"/>
+      <c r="H16" s="104" t="n"/>
+      <c r="I16" s="104" t="n"/>
+      <c r="J16" s="104" t="n"/>
+      <c r="K16" s="104" t="n"/>
+      <c r="L16" s="105" t="n"/>
     </row>
     <row r="17" ht="19.95" customHeight="1" s="27">
       <c r="A17" s="88" t="inlineStr">
@@ -1526,20 +1577,20 @@
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="22" t="n"/>
+      <c r="C17" s="106" t="n"/>
+      <c r="D17" s="104" t="n"/>
+      <c r="E17" s="104" t="n"/>
+      <c r="F17" s="105" t="n"/>
       <c r="G17" s="88" t="inlineStr">
         <is>
           <t>Aspecto</t>
         </is>
       </c>
       <c r="H17" s="22" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="22" t="n"/>
+      <c r="I17" s="106" t="n"/>
+      <c r="J17" s="104" t="n"/>
+      <c r="K17" s="104" t="n"/>
+      <c r="L17" s="105" t="n"/>
     </row>
     <row r="18" ht="28.05" customHeight="1" s="27">
       <c r="A18" s="88" t="inlineStr">
@@ -1548,20 +1599,20 @@
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="22" t="n"/>
+      <c r="C18" s="103" t="n"/>
+      <c r="D18" s="104" t="n"/>
+      <c r="E18" s="104" t="n"/>
+      <c r="F18" s="105" t="n"/>
       <c r="G18" s="88" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
       <c r="H18" s="22" t="n"/>
-      <c r="I18" s="24" t="n"/>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="25" t="n"/>
-      <c r="L18" s="22" t="n"/>
+      <c r="I18" s="103" t="n"/>
+      <c r="J18" s="104" t="n"/>
+      <c r="K18" s="104" t="n"/>
+      <c r="L18" s="105" t="n"/>
     </row>
     <row r="19" ht="19.95" customHeight="1" s="27">
       <c r="A19" s="88" t="inlineStr">
@@ -1570,20 +1621,20 @@
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="22" t="n"/>
+      <c r="C19" s="106" t="n"/>
+      <c r="D19" s="104" t="n"/>
+      <c r="E19" s="104" t="n"/>
+      <c r="F19" s="105" t="n"/>
       <c r="G19" s="88" t="inlineStr">
         <is>
           <t>Coordenadas</t>
         </is>
       </c>
       <c r="H19" s="22" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="25" t="n"/>
-      <c r="L19" s="22" t="n"/>
+      <c r="I19" s="106" t="n"/>
+      <c r="J19" s="104" t="n"/>
+      <c r="K19" s="104" t="n"/>
+      <c r="L19" s="105" t="n"/>
     </row>
     <row r="20" ht="19.95" customHeight="1" s="27">
       <c r="A20" s="88" t="inlineStr">
@@ -1592,20 +1643,20 @@
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="22" t="n"/>
+      <c r="C20" s="106" t="n"/>
+      <c r="D20" s="104" t="n"/>
+      <c r="E20" s="104" t="n"/>
+      <c r="F20" s="105" t="n"/>
       <c r="G20" s="88" t="inlineStr">
         <is>
           <t>Fecha y hora</t>
         </is>
       </c>
       <c r="H20" s="22" t="n"/>
-      <c r="I20" s="32" t="n"/>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="25" t="n"/>
-      <c r="L20" s="22" t="n"/>
+      <c r="I20" s="106" t="n"/>
+      <c r="J20" s="104" t="n"/>
+      <c r="K20" s="104" t="n"/>
+      <c r="L20" s="105" t="n"/>
     </row>
     <row r="21" ht="16.95" customHeight="1" s="27">
       <c r="A21" s="80" t="inlineStr">
@@ -1630,18 +1681,18 @@
       <c r="L21" s="21" t="n"/>
     </row>
     <row r="22" ht="199.95" customHeight="1" s="27">
-      <c r="A22" s="89" t="n"/>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="89" t="n"/>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="22" t="n"/>
+      <c r="A22" s="108" t="n"/>
+      <c r="B22" s="104" t="n"/>
+      <c r="C22" s="104" t="n"/>
+      <c r="D22" s="104" t="n"/>
+      <c r="E22" s="104" t="n"/>
+      <c r="F22" s="105" t="n"/>
+      <c r="G22" s="108" t="n"/>
+      <c r="H22" s="104" t="n"/>
+      <c r="I22" s="104" t="n"/>
+      <c r="J22" s="104" t="n"/>
+      <c r="K22" s="104" t="n"/>
+      <c r="L22" s="105" t="n"/>
     </row>
     <row r="23" ht="19.95" customHeight="1" s="27">
       <c r="A23" s="88" t="inlineStr">
@@ -1650,20 +1701,20 @@
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="22" t="n"/>
+      <c r="C23" s="106" t="n"/>
+      <c r="D23" s="104" t="n"/>
+      <c r="E23" s="104" t="n"/>
+      <c r="F23" s="105" t="n"/>
       <c r="G23" s="88" t="inlineStr">
         <is>
           <t>Aspecto</t>
         </is>
       </c>
       <c r="H23" s="22" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="22" t="n"/>
+      <c r="I23" s="106" t="n"/>
+      <c r="J23" s="104" t="n"/>
+      <c r="K23" s="104" t="n"/>
+      <c r="L23" s="105" t="n"/>
     </row>
     <row r="24" ht="28.05" customHeight="1" s="27">
       <c r="A24" s="88" t="inlineStr">
@@ -1672,20 +1723,20 @@
         </is>
       </c>
       <c r="B24" s="22" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="22" t="n"/>
+      <c r="C24" s="103" t="n"/>
+      <c r="D24" s="104" t="n"/>
+      <c r="E24" s="104" t="n"/>
+      <c r="F24" s="105" t="n"/>
       <c r="G24" s="88" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
       <c r="H24" s="22" t="n"/>
-      <c r="I24" s="24" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="25" t="n"/>
-      <c r="L24" s="22" t="n"/>
+      <c r="I24" s="103" t="n"/>
+      <c r="J24" s="104" t="n"/>
+      <c r="K24" s="104" t="n"/>
+      <c r="L24" s="105" t="n"/>
     </row>
     <row r="25" ht="19.95" customHeight="1" s="27">
       <c r="A25" s="88" t="inlineStr">
@@ -1694,20 +1745,20 @@
         </is>
       </c>
       <c r="B25" s="22" t="n"/>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="22" t="n"/>
+      <c r="C25" s="106" t="n"/>
+      <c r="D25" s="104" t="n"/>
+      <c r="E25" s="104" t="n"/>
+      <c r="F25" s="105" t="n"/>
       <c r="G25" s="88" t="inlineStr">
         <is>
           <t>Coordenadas</t>
         </is>
       </c>
       <c r="H25" s="22" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="25" t="n"/>
-      <c r="L25" s="22" t="n"/>
+      <c r="I25" s="106" t="n"/>
+      <c r="J25" s="104" t="n"/>
+      <c r="K25" s="104" t="n"/>
+      <c r="L25" s="105" t="n"/>
     </row>
     <row r="26" ht="19.95" customHeight="1" s="27">
       <c r="A26" s="88" t="inlineStr">
@@ -1716,20 +1767,20 @@
         </is>
       </c>
       <c r="B26" s="22" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="22" t="n"/>
+      <c r="C26" s="106" t="n"/>
+      <c r="D26" s="104" t="n"/>
+      <c r="E26" s="104" t="n"/>
+      <c r="F26" s="105" t="n"/>
       <c r="G26" s="88" t="inlineStr">
         <is>
           <t>Fecha y hora</t>
         </is>
       </c>
       <c r="H26" s="22" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="25" t="n"/>
-      <c r="L26" s="22" t="n"/>
+      <c r="I26" s="106" t="n"/>
+      <c r="J26" s="104" t="n"/>
+      <c r="K26" s="104" t="n"/>
+      <c r="L26" s="105" t="n"/>
     </row>
     <row r="27" ht="16.95" customHeight="1" s="27">
       <c r="A27" s="80" t="inlineStr">
@@ -1754,18 +1805,18 @@
       <c r="L27" s="21" t="n"/>
     </row>
     <row r="28" ht="199.95" customHeight="1" s="27">
-      <c r="A28" s="89" t="n"/>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="89" t="n"/>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="25" t="n"/>
-      <c r="L28" s="22" t="n"/>
+      <c r="A28" s="108" t="n"/>
+      <c r="B28" s="104" t="n"/>
+      <c r="C28" s="104" t="n"/>
+      <c r="D28" s="104" t="n"/>
+      <c r="E28" s="104" t="n"/>
+      <c r="F28" s="105" t="n"/>
+      <c r="G28" s="108" t="n"/>
+      <c r="H28" s="104" t="n"/>
+      <c r="I28" s="104" t="n"/>
+      <c r="J28" s="104" t="n"/>
+      <c r="K28" s="104" t="n"/>
+      <c r="L28" s="105" t="n"/>
     </row>
     <row r="29" ht="19.95" customHeight="1" s="27">
       <c r="A29" s="88" t="inlineStr">
@@ -1774,20 +1825,20 @@
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="25" t="n"/>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="22" t="n"/>
+      <c r="C29" s="106" t="n"/>
+      <c r="D29" s="104" t="n"/>
+      <c r="E29" s="104" t="n"/>
+      <c r="F29" s="105" t="n"/>
       <c r="G29" s="88" t="inlineStr">
         <is>
           <t>Aspecto</t>
         </is>
       </c>
       <c r="H29" s="22" t="n"/>
-      <c r="I29" s="32" t="n"/>
-      <c r="J29" s="25" t="n"/>
-      <c r="K29" s="25" t="n"/>
-      <c r="L29" s="22" t="n"/>
+      <c r="I29" s="106" t="n"/>
+      <c r="J29" s="104" t="n"/>
+      <c r="K29" s="104" t="n"/>
+      <c r="L29" s="105" t="n"/>
     </row>
     <row r="30" ht="28.05" customHeight="1" s="27">
       <c r="A30" s="88" t="inlineStr">
@@ -1796,20 +1847,20 @@
         </is>
       </c>
       <c r="B30" s="22" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="22" t="n"/>
+      <c r="C30" s="103" t="n"/>
+      <c r="D30" s="104" t="n"/>
+      <c r="E30" s="104" t="n"/>
+      <c r="F30" s="105" t="n"/>
       <c r="G30" s="88" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
       <c r="H30" s="22" t="n"/>
-      <c r="I30" s="24" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
-      <c r="L30" s="22" t="n"/>
+      <c r="I30" s="103" t="n"/>
+      <c r="J30" s="104" t="n"/>
+      <c r="K30" s="104" t="n"/>
+      <c r="L30" s="105" t="n"/>
     </row>
     <row r="31" ht="19.95" customHeight="1" s="27">
       <c r="A31" s="88" t="inlineStr">
@@ -1818,20 +1869,20 @@
         </is>
       </c>
       <c r="B31" s="22" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="25" t="n"/>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="22" t="n"/>
+      <c r="C31" s="106" t="n"/>
+      <c r="D31" s="104" t="n"/>
+      <c r="E31" s="104" t="n"/>
+      <c r="F31" s="105" t="n"/>
       <c r="G31" s="88" t="inlineStr">
         <is>
           <t>Coordenadas</t>
         </is>
       </c>
       <c r="H31" s="22" t="n"/>
-      <c r="I31" s="32" t="n"/>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="25" t="n"/>
-      <c r="L31" s="22" t="n"/>
+      <c r="I31" s="106" t="n"/>
+      <c r="J31" s="104" t="n"/>
+      <c r="K31" s="104" t="n"/>
+      <c r="L31" s="105" t="n"/>
     </row>
     <row r="32" ht="19.95" customHeight="1" s="27">
       <c r="A32" s="88" t="inlineStr">
@@ -1840,23 +1891,23 @@
         </is>
       </c>
       <c r="B32" s="22" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="22" t="n"/>
+      <c r="C32" s="106" t="n"/>
+      <c r="D32" s="104" t="n"/>
+      <c r="E32" s="104" t="n"/>
+      <c r="F32" s="105" t="n"/>
       <c r="G32" s="88" t="inlineStr">
         <is>
           <t>Fecha y hora</t>
         </is>
       </c>
       <c r="H32" s="22" t="n"/>
-      <c r="I32" s="32" t="n"/>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="25" t="n"/>
-      <c r="L32" s="22" t="n"/>
+      <c r="I32" s="106" t="n"/>
+      <c r="J32" s="104" t="n"/>
+      <c r="K32" s="104" t="n"/>
+      <c r="L32" s="105" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="27">
-      <c r="A33" s="94" t="inlineStr">
+      <c r="A33" s="109" t="inlineStr">
         <is>
           <t>Las coordenadas (latitud, longitud) las toma el celular al hacer la foto. Una foto por recuadro, sin recortar ni editar.</t>
         </is>
@@ -1920,20 +1971,20 @@
         </is>
       </c>
       <c r="B36" s="18" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="18" t="n"/>
+      <c r="C36" s="110" t="n"/>
+      <c r="D36" s="111" t="n"/>
+      <c r="E36" s="111" t="n"/>
+      <c r="F36" s="112" t="n"/>
       <c r="G36" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="H36" s="18" t="n"/>
-      <c r="I36" s="19" t="n"/>
-      <c r="J36" s="17" t="n"/>
-      <c r="K36" s="17" t="n"/>
-      <c r="L36" s="18" t="n"/>
+      <c r="I36" s="110" t="n"/>
+      <c r="J36" s="111" t="n"/>
+      <c r="K36" s="111" t="n"/>
+      <c r="L36" s="112" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1" s="27">
       <c r="A37" s="82" t="inlineStr">
@@ -1942,20 +1993,20 @@
         </is>
       </c>
       <c r="B37" s="18" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="18" t="n"/>
+      <c r="C37" s="110" t="n"/>
+      <c r="D37" s="111" t="n"/>
+      <c r="E37" s="111" t="n"/>
+      <c r="F37" s="112" t="n"/>
       <c r="G37" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="H37" s="18" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="17" t="n"/>
-      <c r="L37" s="18" t="n"/>
+      <c r="I37" s="110" t="n"/>
+      <c r="J37" s="111" t="n"/>
+      <c r="K37" s="111" t="n"/>
+      <c r="L37" s="112" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1" s="27">
       <c r="A38" s="82" t="inlineStr">
@@ -1964,20 +2015,20 @@
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="18" t="n"/>
+      <c r="C38" s="110" t="n"/>
+      <c r="D38" s="111" t="n"/>
+      <c r="E38" s="111" t="n"/>
+      <c r="F38" s="112" t="n"/>
       <c r="G38" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="H38" s="18" t="n"/>
-      <c r="I38" s="19" t="n"/>
-      <c r="J38" s="17" t="n"/>
-      <c r="K38" s="17" t="n"/>
-      <c r="L38" s="18" t="n"/>
+      <c r="I38" s="110" t="n"/>
+      <c r="J38" s="111" t="n"/>
+      <c r="K38" s="111" t="n"/>
+      <c r="L38" s="112" t="n"/>
     </row>
     <row r="39" s="27">
       <c r="A39" s="1" t="inlineStr">
@@ -1991,6 +2042,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="101">
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G28:L28"/>
